--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CBA SPAIN.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CBA SPAIN.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CALDERON SUAREZ</t>
+          <t>A. VIEIRA BARRETO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0225</v>
+        <v>0.4483</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1359</v>
+        <v>-0.3232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1134</v>
+        <v>0.7715</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1695</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.6087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3441</v>
+        <v>0.0538</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0829</v>
+        <v>-0.0132</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.159</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0829</v>
+        <v>0.1458</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2524</v>
+        <v>-0.5417</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.4497</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2611</v>
+        <v>-0.092</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4089</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2189</v>
+        <v>-0.3099</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.19</v>
+        <v>0.3867</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VIEIRA BARRETO</t>
+          <t>D. CALDERON SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1946</v>
+        <v>0.0021</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8675</v>
+        <v>-0.1359</v>
       </c>
       <c r="F4" t="n">
-        <v>0.673</v>
+        <v>0.138</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.1695</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6087</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0538</v>
+        <v>0.3441</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0132</v>
+        <v>0.0829</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.159</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1458</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5417</v>
+        <v>-0.2524</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4497</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.092</v>
+        <v>0.2611</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5661</v>
+        <v>-0.3843</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.2189</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2882</v>
+        <v>-0.1654</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7419</v>
+        <v>-0.6927</v>
       </c>
       <c r="E5" t="n">
         <v>0.008200000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7502</v>
+        <v>-0.7009</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7201</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0219</v>
+        <v>0.0274</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>H. GREVELS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.564800000000001</v>
+        <v>-2.5628</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.888800000000001</v>
+        <v>1.5845</v>
       </c>
       <c r="F7" t="n">
-        <v>1.323899999999999</v>
+        <v>-4.147600000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.840400000000001</v>
+        <v>-1.2702</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5732999999999996</v>
+        <v>-5.4535</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.4138</v>
+        <v>4.1833</v>
       </c>
       <c r="J7" t="n">
-        <v>8.571400000000001</v>
+        <v>10.1021</v>
       </c>
       <c r="K7" t="n">
-        <v>9.5962</v>
+        <v>2.3947</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0249</v>
+        <v>7.7075</v>
       </c>
       <c r="M7" t="n">
-        <v>-14.4122</v>
+        <v>-11.3723</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.023099999999999</v>
+        <v>-7.8482</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.388999999999999</v>
+        <v>-3.524</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4086</v>
+        <v>8.523199999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-22.2344</v>
+        <v>-7.7819</v>
       </c>
       <c r="R7" t="n">
-        <v>24.6433</v>
+        <v>16.3052</v>
       </c>
       <c r="S7" t="n">
-        <v>13.9662</v>
+        <v>-3.3985</v>
       </c>
       <c r="T7" t="n">
-        <v>5.9457</v>
+        <v>-3.2532</v>
       </c>
       <c r="U7" t="n">
-        <v>8.0205</v>
+        <v>-0.1457000000000002</v>
       </c>
       <c r="V7" t="n">
-        <v>-14.0995</v>
+        <v>-6.4174</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8282</v>
+        <v>2.5177</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.9277</v>
+        <v>-8.9351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MORALES DAVILA</t>
+          <t>E. COELHO PAULINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.0934</v>
+        <v>-4.7301</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.79</v>
+        <v>-2.8619</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6966000000000001</v>
+        <v>-1.8681</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7649</v>
+        <v>-1.4784</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5267</v>
+        <v>-0.6818</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.2918</v>
+        <v>-0.7966</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5657</v>
+        <v>3.0325</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2578</v>
+        <v>1.8714</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.8236</v>
+        <v>1.1613</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1993</v>
+        <v>-4.5111</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7311000000000001</v>
+        <v>-2.5532</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4681</v>
+        <v>-1.9578</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6676</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.0028</v>
+        <v>-6.6704</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3351</v>
+        <v>5.5586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9742</v>
+        <v>-2.3296</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4787</v>
+        <v>-0.7975</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4955</v>
+        <v>-1.5321</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3132999999999999</v>
+        <v>0.1897</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2571</v>
+        <v>1.5733</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9439</v>
+        <v>-1.3837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. COELHO PAULINO</t>
+          <t>I. MORALES DAVILA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.5353</v>
+        <v>-5.2657</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7433</v>
+        <v>-5.7899</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7921</v>
+        <v>0.5242</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4784</v>
+        <v>-2.7649</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6818</v>
+        <v>1.5267</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7966</v>
+        <v>-4.2918</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0325</v>
+        <v>-1.5657</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8714</v>
+        <v>2.2578</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1613</v>
+        <v>-3.8236</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.5111</v>
+        <v>-1.1993</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5532</v>
+        <v>-0.7311000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9578</v>
+        <v>-0.4681</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1117</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.6704</v>
+        <v>-5.0028</v>
       </c>
       <c r="R9" t="n">
-        <v>5.5586</v>
+        <v>3.3351</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.1347</v>
+        <v>-1.1464</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.6788</v>
+        <v>-0.4787</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4561</v>
+        <v>-0.6677</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1897</v>
+        <v>0.3132999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5733</v>
+        <v>1.2571</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3837</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. GREVELS</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.140700000000001</v>
+        <v>-11.9211</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6584</v>
+        <v>-0.2188999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.4823</v>
+        <v>-11.702</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2702</v>
+        <v>-2.647599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.4535</v>
+        <v>3.8037</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1833</v>
+        <v>-6.4514</v>
       </c>
       <c r="J10" t="n">
-        <v>10.1021</v>
+        <v>26.35</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3947</v>
+        <v>20.0314</v>
       </c>
       <c r="L10" t="n">
-        <v>7.7075</v>
+        <v>6.3187</v>
       </c>
       <c r="M10" t="n">
-        <v>-11.3723</v>
+        <v>-28.9975</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.8482</v>
+        <v>-16.2278</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.524</v>
+        <v>-12.77</v>
       </c>
       <c r="P10" t="n">
-        <v>8.523199999999999</v>
+        <v>-12.4143</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.7819</v>
+        <v>-39.8367</v>
       </c>
       <c r="R10" t="n">
-        <v>16.3052</v>
+        <v>27.4224</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.9765</v>
+        <v>-3.1506</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.4961</v>
+        <v>-3.0908</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4805</v>
+        <v>-0.05980000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.4174</v>
+        <v>6.291399999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5177</v>
+        <v>16.3587</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.9351</v>
+        <v>-10.0671</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.8943</v>
+        <v>-12.0119</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4981000000000009</v>
+        <v>-9.195</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.3923</v>
+        <v>-2.816999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.647599999999999</v>
+        <v>-5.840400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8037</v>
+        <v>0.5732999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.4514</v>
+        <v>-6.4138</v>
       </c>
       <c r="J11" t="n">
-        <v>26.35</v>
+        <v>8.571400000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>20.0314</v>
+        <v>9.5962</v>
       </c>
       <c r="L11" t="n">
-        <v>6.3187</v>
+        <v>-1.0249</v>
       </c>
       <c r="M11" t="n">
-        <v>-28.9975</v>
+        <v>-14.4122</v>
       </c>
       <c r="N11" t="n">
-        <v>-16.2278</v>
+        <v>-9.023099999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.77</v>
+        <v>-5.388999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.4143</v>
+        <v>2.4086</v>
       </c>
       <c r="Q11" t="n">
-        <v>-39.8367</v>
+        <v>-22.2344</v>
       </c>
       <c r="R11" t="n">
-        <v>27.4224</v>
+        <v>24.6433</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.124</v>
+        <v>5.5191</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.373699999999999</v>
+        <v>1.6397</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2496999999999999</v>
+        <v>3.8796</v>
       </c>
       <c r="V11" t="n">
-        <v>6.291399999999999</v>
+        <v>-14.0995</v>
       </c>
       <c r="W11" t="n">
-        <v>16.3587</v>
+        <v>2.8282</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.0671</v>
+        <v>-16.9277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>F. GERONIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.6453</v>
+        <v>-13.015</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2828</v>
+        <v>-11.8722</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.3626</v>
+        <v>-1.1427</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.393</v>
+        <v>-2.4819</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.2433</v>
+        <v>-6.0718</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1499</v>
+        <v>3.5899</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8070000000000004</v>
+        <v>0.2591000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1099999999999999</v>
+        <v>-3.3301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6966999999999999</v>
+        <v>3.5892</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.1999</v>
+        <v>-2.741</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.3534</v>
+        <v>-2.7417</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.8465</v>
+        <v>0.0007999999999999119</v>
       </c>
       <c r="P12" t="n">
-        <v>8.3377</v>
+        <v>-5.5586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.929</v>
+        <v>-11.3024</v>
       </c>
       <c r="R12" t="n">
-        <v>14.2672</v>
+        <v>5.7438</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0451000000000002</v>
+        <v>-1.5122</v>
       </c>
       <c r="T12" t="n">
-        <v>1.581</v>
+        <v>-1.1428</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6257</v>
+        <v>-0.3693999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.5451</v>
+        <v>-3.4624</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0.3138</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.804</v>
+        <v>-3.7763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. GERONIN</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.5512</v>
+        <v>-14.3176</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.2115</v>
+        <v>-7.821399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.339700000000001</v>
+        <v>-6.4961</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4819</v>
+        <v>-10.8143</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.0718</v>
+        <v>-5.08</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5899</v>
+        <v>-5.734400000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2591000000000001</v>
+        <v>12.0829</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.3301</v>
+        <v>13.4195</v>
       </c>
       <c r="L13" t="n">
-        <v>3.5892</v>
+        <v>-1.3366</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.741</v>
+        <v>-22.8972</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.7417</v>
+        <v>-18.4993</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0007999999999999119</v>
+        <v>-4.3979</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.5586</v>
+        <v>-8.523399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3024</v>
+        <v>-37.428</v>
       </c>
       <c r="R13" t="n">
-        <v>5.7438</v>
+        <v>28.9046</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0484</v>
+        <v>-6.2469</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4822</v>
+        <v>-1.6705</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5665</v>
+        <v>-4.5765</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.4624</v>
+        <v>11.2667</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3138</v>
+        <v>19.1942</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7763</v>
+        <v>-7.927099999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.7454</v>
+        <v>-15.3822</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.833300000000001</v>
+        <v>-5.0246</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.9123</v>
+        <v>-10.3574</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.8143</v>
+        <v>-14.393</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.08</v>
+        <v>-11.2433</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.734400000000001</v>
+        <v>-3.1499</v>
       </c>
       <c r="J14" t="n">
-        <v>12.0829</v>
+        <v>0.8070000000000004</v>
       </c>
       <c r="K14" t="n">
-        <v>13.4195</v>
+        <v>0.1099999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3366</v>
+        <v>0.6966999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-22.8972</v>
+        <v>-15.1999</v>
       </c>
       <c r="N14" t="n">
-        <v>-18.4993</v>
+        <v>-11.3534</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.3979</v>
+        <v>-3.8465</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.523399999999999</v>
+        <v>8.3377</v>
       </c>
       <c r="Q14" t="n">
-        <v>-37.428</v>
+        <v>-5.929</v>
       </c>
       <c r="R14" t="n">
-        <v>28.9046</v>
+        <v>14.2672</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.6748</v>
+        <v>-2.7818</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6822</v>
+        <v>-1.1613</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.9926</v>
+        <v>-1.6205</v>
       </c>
       <c r="V14" t="n">
-        <v>11.2667</v>
+        <v>-6.5451</v>
       </c>
       <c r="W14" t="n">
-        <v>19.1942</v>
+        <v>1.2589</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.927099999999999</v>
+        <v>-7.804</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.5685</v>
+        <v>-16.0607</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.999599999999999</v>
+        <v>-10.3367</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.5688</v>
+        <v>-5.7242</v>
       </c>
       <c r="G15" t="n">
         <v>-7.1379</v>
@@ -1624,13 +1624,13 @@
         <v>7.596699999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6179</v>
+        <v>-2.1103</v>
       </c>
       <c r="T15" t="n">
-        <v>0.09200000000000003</v>
+        <v>-0.2449</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.7101</v>
+        <v>-1.8653</v>
       </c>
       <c r="V15" t="n">
         <v>-4.4039</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.8487</v>
+        <v>-18.5272</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.4198</v>
+        <v>-20.3727</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4287</v>
+        <v>1.845699999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.8434</v>
+        <v>-20.9888</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.3578</v>
+        <v>-14.2741</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4856</v>
+        <v>-6.7147</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.7156</v>
+        <v>-2.192000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.7937</v>
+        <v>3.212699999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0783</v>
+        <v>-5.404300000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-10.1277</v>
+        <v>-18.7967</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.563899999999999</v>
+        <v>-17.4866</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.564</v>
+        <v>-1.3103</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1852</v>
+        <v>19.0844</v>
       </c>
       <c r="Q16" t="n">
-        <v>-10.7465</v>
+        <v>-15.9345</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5613</v>
+        <v>35.019</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4785</v>
+        <v>-1.712</v>
       </c>
       <c r="T16" t="n">
-        <v>1.51</v>
+        <v>-3.5021</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.03140000000000015</v>
+        <v>1.7904</v>
       </c>
       <c r="V16" t="n">
-        <v>-6.2987</v>
+        <v>-14.9111</v>
       </c>
       <c r="W16" t="n">
-        <v>-3.4678</v>
+        <v>1.2559</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.8311</v>
+        <v>-16.1673</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.0165</v>
+        <v>-19.6404</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.3755</v>
+        <v>-27.3446</v>
       </c>
       <c r="F17" t="n">
-        <v>2.358999999999999</v>
+        <v>7.7041</v>
       </c>
       <c r="G17" t="n">
-        <v>-20.9888</v>
+        <v>-17.8942</v>
       </c>
       <c r="H17" t="n">
-        <v>-14.2741</v>
+        <v>-21.124</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.7147</v>
+        <v>3.2299</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.192000000000001</v>
+        <v>0.5855999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>3.212699999999999</v>
+        <v>-7.8794</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.404300000000001</v>
+        <v>8.4651</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.7967</v>
+        <v>-18.4803</v>
       </c>
       <c r="N17" t="n">
-        <v>-17.4866</v>
+        <v>-13.2445</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3103</v>
+        <v>-5.235200000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>19.0844</v>
+        <v>-0.7412000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-15.9345</v>
+        <v>-32.9811</v>
       </c>
       <c r="R17" t="n">
-        <v>35.019</v>
+        <v>32.2397</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2016</v>
+        <v>-7.6128</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.5051</v>
+        <v>-5.0173</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3036</v>
+        <v>-2.5956</v>
       </c>
       <c r="V17" t="n">
-        <v>-14.9111</v>
+        <v>6.6078</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2559</v>
+        <v>10.068</v>
       </c>
       <c r="X17" t="n">
-        <v>-16.1673</v>
+        <v>-3.4602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.3705</v>
+        <v>-20.4989</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.3402</v>
+        <v>-15.591</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.0299</v>
+        <v>-4.907699999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.010200000000001</v>
+        <v>-16.2212</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2724</v>
+        <v>-6.6188</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7376</v>
+        <v>-9.6021</v>
       </c>
       <c r="J18" t="n">
-        <v>8.7918</v>
+        <v>-6.069199999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>8.8736</v>
+        <v>-0.3751</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.08179999999999998</v>
+        <v>-5.6944</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.802</v>
+        <v>-10.1522</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.1461</v>
+        <v>-6.2437</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.656</v>
+        <v>-3.9082</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.5996</v>
+        <v>-1.4822</v>
       </c>
       <c r="Q18" t="n">
-        <v>-27.6076</v>
+        <v>-10.0053</v>
       </c>
       <c r="R18" t="n">
-        <v>15.0083</v>
+        <v>8.523199999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>4.993300000000001</v>
+        <v>-1.7275</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5331</v>
+        <v>-1.0894</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4601</v>
+        <v>-0.638</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.754200000000001</v>
+        <v>-1.0674</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9421999999999999</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.6964</v>
+        <v>-2.6408</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.4098</v>
+        <v>-20.905</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.5271</v>
+        <v>-18.6515</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.8828</v>
+        <v>-2.2535</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.2212</v>
+        <v>-12.8434</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.6188</v>
+        <v>-11.3578</v>
       </c>
       <c r="I19" t="n">
-        <v>-9.6021</v>
+        <v>-1.4856</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.069199999999999</v>
+        <v>-2.7156</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3751</v>
+        <v>-3.7937</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.6944</v>
+        <v>1.0783</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.1522</v>
+        <v>-10.1277</v>
       </c>
       <c r="N19" t="n">
-        <v>-6.2437</v>
+        <v>-7.563899999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.9082</v>
+        <v>-2.564</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4822</v>
+        <v>-0.1852</v>
       </c>
       <c r="Q19" t="n">
-        <v>-10.0053</v>
+        <v>-10.7465</v>
       </c>
       <c r="R19" t="n">
-        <v>8.523199999999999</v>
+        <v>10.5613</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.6386</v>
+        <v>-1.5776</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.0257</v>
+        <v>-1.7219</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.6131</v>
+        <v>0.1442999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0674</v>
+        <v>-6.2987</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5733</v>
+        <v>-3.4678</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6408</v>
+        <v>-2.8311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>-24.2494</v>
+        <v>-27.1445</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.4876</v>
+        <v>-17.7017</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.761299999999999</v>
+        <v>-9.4429</v>
       </c>
       <c r="G20" t="n">
-        <v>-24.4856</v>
+        <v>-4.010200000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.7479</v>
+        <v>-1.2724</v>
       </c>
       <c r="I20" t="n">
-        <v>-11.7378</v>
+        <v>-2.7376</v>
       </c>
       <c r="J20" t="n">
-        <v>3.337400000000001</v>
+        <v>8.7918</v>
       </c>
       <c r="K20" t="n">
-        <v>4.234</v>
+        <v>8.8736</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8966000000000005</v>
+        <v>-0.08179999999999998</v>
       </c>
       <c r="M20" t="n">
-        <v>-27.8229</v>
+        <v>-12.802</v>
       </c>
       <c r="N20" t="n">
-        <v>-16.9819</v>
+        <v>-10.1461</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.8411</v>
+        <v>-2.656</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.632000000000001</v>
+        <v>-12.5996</v>
       </c>
       <c r="Q20" t="n">
-        <v>-39.466</v>
+        <v>-27.6076</v>
       </c>
       <c r="R20" t="n">
-        <v>34.8341</v>
+        <v>15.0083</v>
       </c>
       <c r="S20" t="n">
-        <v>6.1295</v>
+        <v>-0.7809</v>
       </c>
       <c r="T20" t="n">
-        <v>5.8577</v>
+        <v>0.1718999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2721000000000001</v>
+        <v>-0.9527</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2612</v>
+        <v>-9.754200000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>14.7835</v>
+        <v>0.9421999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-16.0447</v>
+        <v>-10.6964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>-24.9531</v>
+        <v>-31.8264</v>
       </c>
       <c r="E21" t="n">
-        <v>-29.5765</v>
+        <v>-23.0486</v>
       </c>
       <c r="F21" t="n">
-        <v>4.6235</v>
+        <v>-8.777699999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-17.8942</v>
+        <v>-24.4856</v>
       </c>
       <c r="H21" t="n">
-        <v>-21.124</v>
+        <v>-12.7479</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2299</v>
+        <v>-11.7378</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5855999999999999</v>
+        <v>3.337400000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.8794</v>
+        <v>4.234</v>
       </c>
       <c r="L21" t="n">
-        <v>8.4651</v>
+        <v>-0.8966000000000005</v>
       </c>
       <c r="M21" t="n">
-        <v>-18.4803</v>
+        <v>-27.8229</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.2445</v>
+        <v>-16.9819</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.235200000000001</v>
+        <v>-10.8411</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7412000000000001</v>
+        <v>-4.632000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-32.9811</v>
+        <v>-39.466</v>
       </c>
       <c r="R21" t="n">
-        <v>32.2397</v>
+        <v>34.8341</v>
       </c>
       <c r="S21" t="n">
-        <v>-12.9256</v>
+        <v>-1.4473</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.249099999999999</v>
+        <v>-1.7031</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.676299999999999</v>
+        <v>0.2555999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>6.6078</v>
+        <v>-1.2612</v>
       </c>
       <c r="W21" t="n">
-        <v>10.068</v>
+        <v>14.7835</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.4602</v>
+        <v>-16.0447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>-60.4766</v>
+        <v>-51.6937</v>
       </c>
       <c r="E22" t="n">
-        <v>-52.6492</v>
+        <v>-42.4983</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.827199999999999</v>
+        <v>-9.195300000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-29.0281</v>
+        <v>-36.7123</v>
       </c>
       <c r="H22" t="n">
-        <v>-27.9065</v>
+        <v>-36.6858</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.121800000000001</v>
+        <v>-0.02639999999999842</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.6856</v>
+        <v>-0.8807</v>
       </c>
       <c r="K22" t="n">
-        <v>-15.2217</v>
+        <v>-9.966700000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4639999999999997</v>
+        <v>9.085900000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-13.3426</v>
+        <v>-35.8316</v>
       </c>
       <c r="N22" t="n">
-        <v>-12.6847</v>
+        <v>-26.7191</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6578000000000002</v>
+        <v>-9.112299999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-18.8992</v>
+        <v>-14.6377</v>
       </c>
       <c r="Q22" t="n">
-        <v>-44.0982</v>
+        <v>-53.548</v>
       </c>
       <c r="R22" t="n">
-        <v>25.1986</v>
+        <v>38.9101</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.409</v>
+        <v>-10.478</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.8231</v>
+        <v>-7.8948</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.5856</v>
+        <v>-2.5834</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1397</v>
+        <v>10.1343</v>
       </c>
       <c r="W22" t="n">
-        <v>11.9581</v>
+        <v>19.8251</v>
       </c>
       <c r="X22" t="n">
-        <v>-14.0978</v>
+        <v>-9.6907</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>-66.3634</v>
+        <v>-54.4495</v>
       </c>
       <c r="E23" t="n">
-        <v>-53.6217</v>
+        <v>-50.1778</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.7416</v>
+        <v>-4.271499999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-36.7123</v>
+        <v>-29.0281</v>
       </c>
       <c r="H23" t="n">
-        <v>-36.6858</v>
+        <v>-27.9065</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.02639999999999842</v>
+        <v>-1.121800000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8807</v>
+        <v>-15.6856</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.966700000000001</v>
+        <v>-15.2217</v>
       </c>
       <c r="L23" t="n">
-        <v>9.085900000000001</v>
+        <v>-0.4639999999999997</v>
       </c>
       <c r="M23" t="n">
-        <v>-35.8316</v>
+        <v>-13.3426</v>
       </c>
       <c r="N23" t="n">
-        <v>-26.7191</v>
+        <v>-12.6847</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.112299999999999</v>
+        <v>-0.6578000000000002</v>
       </c>
       <c r="P23" t="n">
-        <v>-14.6377</v>
+        <v>-18.8992</v>
       </c>
       <c r="Q23" t="n">
-        <v>-53.548</v>
+        <v>-44.0982</v>
       </c>
       <c r="R23" t="n">
-        <v>38.9101</v>
+        <v>25.1986</v>
       </c>
       <c r="S23" t="n">
-        <v>-25.148</v>
+        <v>-4.3818</v>
       </c>
       <c r="T23" t="n">
-        <v>-19.0182</v>
+        <v>-2.3521</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.1295</v>
+        <v>-2.0298</v>
       </c>
       <c r="V23" t="n">
-        <v>10.1343</v>
+        <v>-2.1397</v>
       </c>
       <c r="W23" t="n">
-        <v>19.8251</v>
+        <v>11.9581</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.6907</v>
+        <v>-14.0978</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>-77.6045</v>
+        <v>-72.1973</v>
       </c>
       <c r="E24" t="n">
-        <v>-61.5217</v>
+        <v>-58.2007</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.0828</v>
+        <v>-13.9966</v>
       </c>
       <c r="G24" t="n">
         <v>-42.1006</v>
@@ -2326,13 +2326,13 @@
         <v>37.0574</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.1367</v>
+        <v>-5.7295</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.3834</v>
+        <v>-4.0627</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.7529</v>
+        <v>-1.6667</v>
       </c>
       <c r="V24" t="n">
         <v>-18.0679</v>
@@ -2359,13 +2359,13 @@
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>-400.2885</v>
+        <v>-385.6904</v>
       </c>
       <c r="E25" t="n">
-        <v>-300.6009</v>
+        <v>-297.7507</v>
       </c>
       <c r="F25" t="n">
-        <v>-99.6865</v>
+        <v>-87.93900000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-226.2434</v>
@@ -2377,13 +2377,13 @@
         <v>-52.1771</v>
       </c>
       <c r="J25" t="n">
-        <v>59.8344</v>
+        <v>59.83440000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>33.15679999999999</v>
+        <v>33.1568</v>
       </c>
       <c r="L25" t="n">
-        <v>26.6779</v>
+        <v>26.67789999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-286.079</v>
@@ -2401,19 +2401,19 @@
         <v>-425.7885</v>
       </c>
       <c r="R25" t="n">
-        <v>373.5374</v>
+        <v>373.5373999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-68.1709</v>
+        <v>-53.5711</v>
       </c>
       <c r="T25" t="n">
-        <v>-40.9688</v>
+        <v>-38.1191</v>
       </c>
       <c r="U25" t="n">
-        <v>-27.2011</v>
+        <v>-15.4522</v>
       </c>
       <c r="V25" t="n">
-        <v>-53.6248</v>
+        <v>-53.62480000000001</v>
       </c>
       <c r="W25" t="n">
         <v>106.3221</v>
